--- a/r5-aist-trustworthyai-main/CodeSystem-eu-ai-artifact-type-cs.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-eu-ai-artifact-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/CodeSystem-eu-ai-artifact-type-cs.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-eu-ai-artifact-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/CodeSystem-eu-ai-artifact-type-cs.xlsx
+++ b/r5-aist-trustworthyai-main/CodeSystem-eu-ai-artifact-type-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
